--- a/survey_templates/048_e_bike_customer_survey--survey_templates.xlsx
+++ b/survey_templates/048_e_bike_customer_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -920,7 +920,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>agree with our terms and conditions</t>
+          <t>E Bike Agree Terms</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -938,7 +938,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>e_bike_terms_and_conditions</t>
+          <t>e_bike_terms_and_conditions_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -966,7 +966,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>uploads</t>
+          <t>E Bike Upload Uploads Uploads</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -989,7 +989,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>additional comments</t>
+          <t>E Bike Additional Comments Uploads</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>agree with our terms and conditions</t>
+          <t>E Bike Agree Terms Uploads</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>agree with our terms and conditions</t>
+          <t>E Bike Agree Conditions</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1106,8 +1106,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1135,12 +1135,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1152,12 +1152,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1169,12 +1169,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'not_sure'}</t>
+          <t>not_sure</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Not Sure'}</t>
+          <t>Not Sure</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true,_'required':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True, 'required': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1203,12 +1203,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1220,12 +1220,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'decline'}</t>
+          <t>decline</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Decline'}</t>
+          <t>Decline</t>
         </is>
       </c>
     </row>
@@ -1339,12 +1339,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1356,12 +1356,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1373,12 +1373,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'decline'}</t>
+          <t>decline</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Decline'}</t>
+          <t>Decline</t>
         </is>
       </c>
     </row>
